--- a/DateBase/orders/Nhat 48_2026-3-15.xlsx
+++ b/DateBase/orders/Nhat 48_2026-3-15.xlsx
@@ -778,6 +778,9 @@
       <c r="C41" t="str">
         <v>734_乒乓菊红_undefined_undefined_1bunch</v>
       </c>
+      <c r="F41" t="str">
+        <v>10</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
@@ -836,7 +839,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>0100100148710155106141010281068815101515401015151510101515101010201015100</v>
+        <v>01001001487101551061410102810688151015154010151515101015151010102010151010</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Nhat 48_2026-3-15.xlsx
+++ b/DateBase/orders/Nhat 48_2026-3-15.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L41"/>
+  <dimension ref="A1:L45"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -782,9 +782,44 @@
         <v>10</v>
       </c>
     </row>
+    <row r="42">
+      <c r="C42" t="str">
+        <v>492_细米花_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F42" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="str">
+        <v>9</v>
+      </c>
+      <c r="C43" t="str">
+        <v>774_紫娇花_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F43" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="C44" t="str">
+        <v>526_大刺秦_Eryngium_undefined_1bunch</v>
+      </c>
+      <c r="F44" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="C45" t="str">
+        <v>447_黄金球_craspedia_undefined_1bunch</v>
+      </c>
+      <c r="F45" t="str">
+        <v>10</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L41"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L45"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -839,7 +874,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>01001001487101551061410102810688151015154010151515101015151010102010151010</v>
+        <v>010010014871015510614101028106881510151540101515151010151510101020101510101010510</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Nhat 48_2026-3-15.xlsx
+++ b/DateBase/orders/Nhat 48_2026-3-15.xlsx
@@ -876,6 +876,9 @@
       <c r="G2" t="str">
         <v>010010014871015510614101028106881510151540101515151010151510101020101510101010510</v>
       </c>
+      <c r="H2" t="str">
+        <v>CNY</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
